--- a/rtt_bursts_tunaveis.xlsx
+++ b/rtt_bursts_tunaveis.xlsx
@@ -476,22 +476,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00:009.9</t>
+          <t>00:010.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>984</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -533,27 +533,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00:019.9</t>
+          <t>00:020.2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>9.04</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -583,34 +583,34 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:030.0</t>
+          <t>00:030.1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>25.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -647,27 +647,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00:040.1</t>
+          <t>00:039.7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>6.12</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -687,44 +687,44 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00:049.8</t>
+          <t>00:050.1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -754,34 +754,34 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00:059.8</t>
+          <t>01:000.0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
@@ -823,22 +823,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>22.7</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>72</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
@@ -880,22 +880,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>22.4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14.45</t>
+          <t>6.43</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -925,34 +925,34 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:029.8</t>
+          <t>01:030.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>6.49</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -982,34 +982,34 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01:040.0</t>
+          <t>01:040.3</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>25.4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1039,24 +1039,24 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01:049.9</t>
+          <t>01:050.0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1096,34 +1096,34 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:059.7</t>
+          <t>01:060.0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26.9</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1153,34 +1153,34 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02:010.2</t>
+          <t>02:010.0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>26.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>6.82</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1222,22 +1222,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.44</t>
+          <t>7.83</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1274,27 +1274,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02:030.0</t>
+          <t>02:029.7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>29.9</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Normal/Residual</t>
+          <t>DDoS Burst</t>
         </is>
       </c>
     </row>
@@ -1336,22 +1336,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1381,34 +1381,34 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>DDoS Burst</t>
+          <t>Normal/Residual</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02:050.1</t>
+          <t>02:050.0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>20.5</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>20.7</t>
-        </is>
-      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1445,27 +1445,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02:055.1</t>
+          <t>02:054.9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20.8</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
